--- a/data/QLD_properties.xlsx
+++ b/data/QLD_properties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\UNIMELB\outbreaksimulator\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thaophuongl\Documents\HASTE_CODE\OutbreakSimulator\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9265C4E0-2759-4C29-A55A-DF461A64D999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73991558-6F3A-4F55-B3EF-C894440DE2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E264DCFB-2E54-41D3-AA9C-B1867134B6AE}"/>
+    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E264DCFB-2E54-41D3-AA9C-B1867134B6AE}"/>
   </bookViews>
   <sheets>
     <sheet name="PoultryData" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="98">
   <si>
     <t>Region Type</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>based on the main LGAs with &gt;=3 number of poultry businesses</t>
+  </si>
+  <si>
+    <t>breeder</t>
   </si>
 </sst>
 </file>
@@ -3759,158 +3762,470 @@
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
+      <c r="A74" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" t="s">
+        <v>97</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E74" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
+      <c r="A75" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75" t="s">
+        <v>97</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
+      <c r="A76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="s">
+        <v>97</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
+      <c r="A77" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" t="s">
+        <v>97</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E77" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
+      <c r="A78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>97</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E78" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
+      <c r="A79" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" t="s">
+        <v>97</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E79" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-    </row>
-    <row r="81" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-    </row>
-    <row r="82" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-    </row>
-    <row r="83" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-    </row>
-    <row r="84" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-    </row>
-    <row r="85" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-    </row>
-    <row r="86" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-    </row>
-    <row r="87" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-    </row>
-    <row r="88" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-    </row>
-    <row r="89" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-    </row>
-    <row r="90" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-    </row>
-    <row r="91" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-    </row>
-    <row r="92" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-    </row>
-    <row r="93" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-    </row>
-    <row r="94" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-    </row>
-    <row r="95" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-    </row>
-    <row r="96" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-    </row>
-    <row r="97" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-    </row>
-    <row r="98" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" t="s">
+        <v>97</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E80" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>4</v>
+      </c>
+      <c r="B81" t="s">
+        <v>21</v>
+      </c>
+      <c r="C81" t="s">
+        <v>97</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B82" t="s">
+        <v>22</v>
+      </c>
+      <c r="C82" t="s">
+        <v>97</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>4</v>
+      </c>
+      <c r="B83" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" t="s">
+        <v>97</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>4</v>
+      </c>
+      <c r="B84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" t="s">
+        <v>97</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E84" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>4</v>
+      </c>
+      <c r="B85" t="s">
+        <v>25</v>
+      </c>
+      <c r="C85" t="s">
+        <v>97</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E85" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>4</v>
+      </c>
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" t="s">
+        <v>97</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E86" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87" t="s">
+        <v>97</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E87" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>4</v>
+      </c>
+      <c r="B88" t="s">
+        <v>28</v>
+      </c>
+      <c r="C88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E88" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>4</v>
+      </c>
+      <c r="B89" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" t="s">
+        <v>97</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>4</v>
+      </c>
+      <c r="B90" t="s">
+        <v>30</v>
+      </c>
+      <c r="C90" t="s">
+        <v>97</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E90" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>4</v>
+      </c>
+      <c r="B91" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" t="s">
+        <v>97</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E91" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>4</v>
+      </c>
+      <c r="B92" t="s">
+        <v>32</v>
+      </c>
+      <c r="C92" t="s">
+        <v>97</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E92" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>4</v>
+      </c>
+      <c r="B93" t="s">
+        <v>33</v>
+      </c>
+      <c r="C93" t="s">
+        <v>97</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E93" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>4</v>
+      </c>
+      <c r="B94" t="s">
+        <v>34</v>
+      </c>
+      <c r="C94" t="s">
+        <v>97</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E94" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>4</v>
+      </c>
+      <c r="B95" t="s">
+        <v>35</v>
+      </c>
+      <c r="C95" t="s">
+        <v>97</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E95" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>4</v>
+      </c>
+      <c r="B96" t="s">
+        <v>36</v>
+      </c>
+      <c r="C96" t="s">
+        <v>97</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>4</v>
+      </c>
+      <c r="B97" t="s">
+        <v>37</v>
+      </c>
+      <c r="C97" t="s">
+        <v>97</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E97" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
     </row>
-    <row r="100" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
     </row>
-    <row r="106" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
     </row>
-    <row r="109" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
     </row>

--- a/data/QLD_properties.xlsx
+++ b/data/QLD_properties.xlsx
@@ -5,20 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thaophuongl\Documents\HASTE_CODE\OutbreakSimulator\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\UNIMELB\outbreaksimulator\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73991558-6F3A-4F55-B3EF-C894440DE2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597368DF-7C46-46E7-9311-57C93CA2FC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E264DCFB-2E54-41D3-AA9C-B1867134B6AE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E264DCFB-2E54-41D3-AA9C-B1867134B6AE}"/>
   </bookViews>
   <sheets>
-    <sheet name="PoultryData" sheetId="1" r:id="rId1"/>
+    <sheet name="PoultryAgTrends" sheetId="8" r:id="rId1"/>
     <sheet name="PoultryCustom" sheetId="7" r:id="rId2"/>
-    <sheet name="Notes" sheetId="3" r:id="rId3"/>
+    <sheet name="PoultryData" sheetId="1" r:id="rId3"/>
+    <sheet name="Notes" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PoultryData!$A$1:$E$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PoultryData!$A$1:$E$222</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="105">
   <si>
     <t>Region Type</t>
   </si>
@@ -319,9 +320,6 @@
     <t>Doomadgee</t>
   </si>
   <si>
-    <t>Agriculural businesses per LGA</t>
-  </si>
-  <si>
     <t>https://qldspatial.information.qld.gov.au/catalogue/custom/detail.page?fid={97C1FDB9-EB25-47BB-8DF1-AFD23CD54F4B}</t>
   </si>
   <si>
@@ -335,6 +333,30 @@
   </si>
   <si>
     <t>breeder</t>
+  </si>
+  <si>
+    <t>Agriculural businesses per LGA (not in use)</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>Postcode</t>
+  </si>
+  <si>
+    <t>layer</t>
+  </si>
+  <si>
+    <t>PoultryAgTrends</t>
+  </si>
+  <si>
+    <t>https://qldspatial.information.qld.gov.au/AGTrendsSpatial/</t>
+  </si>
+  <si>
+    <t>Extracted egg production (layers) and egg processing facilities</t>
   </si>
 </sst>
 </file>
@@ -733,1779 +755,2572 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC8E976-27F5-4CF2-963C-1DA4DC754C80}">
-  <dimension ref="A1:E222"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{160FB0B4-4999-4257-8236-B07121A9A763}">
+  <dimension ref="A1:G111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="34.75" customWidth="1"/>
-    <col min="3" max="3" width="87.25" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
-    <col min="5" max="5" width="27.75" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="13.625" customWidth="1"/>
+    <col min="4" max="4" width="13.125" customWidth="1"/>
+    <col min="5" max="5" width="30.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>152.13369399999999</v>
+      </c>
+      <c r="B2">
+        <v>-27.605029000224501</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2">
-        <v>35.49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>4344</v>
+      </c>
+      <c r="E2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>151.33101199999999</v>
+      </c>
+      <c r="B3">
+        <v>-27.849479000220001</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3">
-        <v>28.18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>4352</v>
+      </c>
+      <c r="E3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>145.40789100000001</v>
+      </c>
+      <c r="B4">
+        <v>-17.407694000460701</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4">
-        <v>17.920000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>4887</v>
+      </c>
+      <c r="E4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>151.67320599999999</v>
+      </c>
+      <c r="B5">
+        <v>-27.777369000221299</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5">
-        <v>15.77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>4358</v>
+      </c>
+      <c r="E5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>151.70426</v>
+      </c>
+      <c r="B6">
+        <v>-27.8064990002208</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6">
-        <v>13.93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>4358</v>
+      </c>
+      <c r="E6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>151.702369</v>
+      </c>
+      <c r="B7">
+        <v>-27.804535000220799</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7">
-        <v>13.87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>4358</v>
+      </c>
+      <c r="E7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>151.650654</v>
+      </c>
+      <c r="B8">
+        <v>-27.716723000222402</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8">
-        <v>13.09</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
+        <v>100</v>
+      </c>
+      <c r="D8">
+        <v>4356</v>
+      </c>
+      <c r="E8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>151.49424999999999</v>
+      </c>
+      <c r="B9">
+        <v>-27.304320000230199</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9">
-        <v>12.31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>4404</v>
+      </c>
+      <c r="E9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>153.03034099999999</v>
+      </c>
+      <c r="B10">
+        <v>-26.563082000244599</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10">
-        <v>11.29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
+        <v>100</v>
+      </c>
+      <c r="D10">
+        <v>4561</v>
+      </c>
+      <c r="E10" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>152.99228299999999</v>
+      </c>
+      <c r="B11">
+        <v>-27.248699000231301</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11">
-        <v>10.08</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>4503</v>
+      </c>
+      <c r="E11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>150.647401</v>
+      </c>
+      <c r="B12">
+        <v>-23.097579000318401</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12">
-        <v>9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
+        <v>100</v>
+      </c>
+      <c r="D12">
+        <v>4703</v>
+      </c>
+      <c r="E12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>152.712862</v>
+      </c>
+      <c r="B13">
+        <v>-26.027349000255299</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13">
-        <v>8.89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>4570</v>
+      </c>
+      <c r="E13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>152.3399</v>
+      </c>
+      <c r="B14">
+        <v>-27.5499540002256</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14">
-        <v>6.81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
-        <v>27</v>
+        <v>100</v>
+      </c>
+      <c r="D14">
+        <v>4343</v>
+      </c>
+      <c r="E14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>150.37215499999999</v>
+      </c>
+      <c r="B15">
+        <v>-23.7222230003043</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15">
-        <v>6.34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
+        <v>100</v>
+      </c>
+      <c r="D15">
+        <v>4714</v>
+      </c>
+      <c r="E15" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>152.56974</v>
+      </c>
+      <c r="B16">
+        <v>-26.939530000237301</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16">
-        <v>6.21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
-        <v>29</v>
+        <v>100</v>
+      </c>
+      <c r="D16">
+        <v>4515</v>
+      </c>
+      <c r="E16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>153.330929</v>
+      </c>
+      <c r="B17">
+        <v>-27.7901050002211</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17">
-        <v>5.69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" t="s">
-        <v>30</v>
+        <v>100</v>
+      </c>
+      <c r="D17">
+        <v>4208</v>
+      </c>
+      <c r="E17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>152.638881</v>
+      </c>
+      <c r="B18">
+        <v>-25.517296000265802</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18">
-        <v>5.45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>31</v>
+        <v>100</v>
+      </c>
+      <c r="D18">
+        <v>4650</v>
+      </c>
+      <c r="E18" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>148.593536</v>
+      </c>
+      <c r="B19">
+        <v>-28.0315110002166</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19">
-        <v>4.87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
+        <v>100</v>
+      </c>
+      <c r="D19">
+        <v>4487</v>
+      </c>
+      <c r="E19" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>150.626991</v>
+      </c>
+      <c r="B20">
+        <v>-26.779322000240398</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
+        <v>100</v>
+      </c>
+      <c r="D20">
+        <v>4413</v>
+      </c>
+      <c r="E20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>152.84199699999999</v>
+      </c>
+      <c r="B21">
+        <v>-26.786202000240198</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" t="s">
-        <v>34</v>
+        <v>100</v>
+      </c>
+      <c r="D21">
+        <v>4519</v>
+      </c>
+      <c r="E21" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>151.848929</v>
+      </c>
+      <c r="B22">
+        <v>-27.8912860002192</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
-        <v>35</v>
+        <v>100</v>
+      </c>
+      <c r="D22">
+        <v>4361</v>
+      </c>
+      <c r="E22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>152.85862</v>
+      </c>
+      <c r="B23">
+        <v>-26.764531000240702</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" t="s">
-        <v>36</v>
+        <v>100</v>
+      </c>
+      <c r="D23">
+        <v>4552</v>
+      </c>
+      <c r="E23" t="s">
+        <v>101</v>
+      </c>
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>150.360815</v>
+      </c>
+      <c r="B24">
+        <v>-28.5345820002075</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
-        <v>37</v>
+        <v>100</v>
+      </c>
+      <c r="D24">
+        <v>4390</v>
+      </c>
+      <c r="E24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>153.25362799999999</v>
+      </c>
+      <c r="B25">
+        <v>-27.591524000224801</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25">
-        <v>3.26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
-        <v>38</v>
+        <v>100</v>
+      </c>
+      <c r="D25">
+        <v>4165</v>
+      </c>
+      <c r="E25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>152.654752</v>
+      </c>
+      <c r="B26">
+        <v>-26.322122000249401</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" t="s">
-        <v>39</v>
+        <v>100</v>
+      </c>
+      <c r="D26">
+        <v>4570</v>
+      </c>
+      <c r="E26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>153.043779</v>
+      </c>
+      <c r="B27">
+        <v>-27.504252000226401</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27">
-        <v>2.4700000000000002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" t="s">
-        <v>40</v>
+        <v>100</v>
+      </c>
+      <c r="D27">
+        <v>4123</v>
+      </c>
+      <c r="E27" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>148.88321199999999</v>
+      </c>
+      <c r="B28">
+        <v>-23.5715440003077</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" t="s">
-        <v>41</v>
+        <v>100</v>
+      </c>
+      <c r="D28">
+        <v>4717</v>
+      </c>
+      <c r="E28" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>151.20209299999999</v>
+      </c>
+      <c r="B29">
+        <v>-27.8448580002201</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>42</v>
+        <v>100</v>
+      </c>
+      <c r="D29">
+        <v>4357</v>
+      </c>
+      <c r="E29" t="s">
+        <v>101</v>
+      </c>
+      <c r="F29" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>151.203003</v>
+      </c>
+      <c r="B30">
+        <v>-27.820974000220499</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" t="s">
-        <v>43</v>
+        <v>100</v>
+      </c>
+      <c r="D30">
+        <v>4357</v>
+      </c>
+      <c r="E30" t="s">
+        <v>101</v>
+      </c>
+      <c r="F30" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>151.32980800000001</v>
+      </c>
+      <c r="B31">
+        <v>-27.844997000220101</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" t="s">
-        <v>44</v>
+        <v>100</v>
+      </c>
+      <c r="D31">
+        <v>4352</v>
+      </c>
+      <c r="E31" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>152.81840199999999</v>
+      </c>
+      <c r="B32">
+        <v>-27.183512000232501</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" t="s">
-        <v>45</v>
+        <v>100</v>
+      </c>
+      <c r="D32">
+        <v>4521</v>
+      </c>
+      <c r="E32" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>151.93595999999999</v>
+      </c>
+      <c r="B33">
+        <v>-26.078304000254299</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
-      </c>
-      <c r="D33" s="3"/>
-      <c r="E33">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" t="s">
-        <v>46</v>
+        <v>100</v>
+      </c>
+      <c r="D33">
+        <v>4605</v>
+      </c>
+      <c r="E33" t="s">
+        <v>101</v>
+      </c>
+      <c r="F33" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>152.68953099999999</v>
+      </c>
+      <c r="B34">
+        <v>-26.267129000250499</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
-      </c>
-      <c r="D34" s="3"/>
-      <c r="E34">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" t="s">
-        <v>47</v>
+        <v>100</v>
+      </c>
+      <c r="D34">
+        <v>4570</v>
+      </c>
+      <c r="E34" t="s">
+        <v>101</v>
+      </c>
+      <c r="F34" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>153.26206500000001</v>
+      </c>
+      <c r="B35">
+        <v>-27.620805000224198</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
-      </c>
-      <c r="D35" s="3"/>
-      <c r="E35">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" t="s">
-        <v>48</v>
+        <v>100</v>
+      </c>
+      <c r="D35">
+        <v>4165</v>
+      </c>
+      <c r="E35" t="s">
+        <v>101</v>
+      </c>
+      <c r="F35" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>142.21446599999999</v>
+      </c>
+      <c r="B36">
+        <v>-20.6528610003765</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
-      </c>
-      <c r="D36" s="3"/>
-      <c r="E36">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" t="s">
-        <v>49</v>
+        <v>100</v>
+      </c>
+      <c r="D36">
+        <v>4816</v>
+      </c>
+      <c r="E36" t="s">
+        <v>101</v>
+      </c>
+      <c r="F36" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>152.75506799999999</v>
+      </c>
+      <c r="B37">
+        <v>-26.521508000245401</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" s="3"/>
-      <c r="E37">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" t="s">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="D37">
+        <v>4574</v>
+      </c>
+      <c r="E37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>151.79781</v>
+      </c>
+      <c r="B38">
+        <v>-26.785578000240299</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" s="3"/>
-      <c r="E38">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" t="s">
-        <v>51</v>
+        <v>100</v>
+      </c>
+      <c r="D38">
+        <v>4615</v>
+      </c>
+      <c r="E38" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>152.93462299999999</v>
+      </c>
+      <c r="B39">
+        <v>-27.951346000218098</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
-      </c>
-      <c r="D39" s="3"/>
-      <c r="E39">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" t="s">
-        <v>52</v>
+        <v>100</v>
+      </c>
+      <c r="D39">
+        <v>4285</v>
+      </c>
+      <c r="E39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>152.70493099999999</v>
+      </c>
+      <c r="B40">
+        <v>-26.511203000245601</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" s="3"/>
-      <c r="E40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" t="s">
-        <v>53</v>
+        <v>100</v>
+      </c>
+      <c r="D40">
+        <v>4570</v>
+      </c>
+      <c r="E40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>152.27760000000001</v>
+      </c>
+      <c r="B41">
+        <v>-27.5674190002253</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
-      </c>
-      <c r="D41" s="3"/>
-      <c r="E41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" t="s">
-        <v>54</v>
+        <v>100</v>
+      </c>
+      <c r="D41">
+        <v>4343</v>
+      </c>
+      <c r="E41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>150.73611700000001</v>
+      </c>
+      <c r="B42">
+        <v>-23.134999000317599</v>
       </c>
       <c r="C42" t="s">
-        <v>95</v>
-      </c>
-      <c r="D42" s="3"/>
-      <c r="E42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" t="s">
-        <v>55</v>
+        <v>100</v>
+      </c>
+      <c r="D42">
+        <v>4703</v>
+      </c>
+      <c r="E42" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>149.17377999999999</v>
+      </c>
+      <c r="B43">
+        <v>-21.117365000365101</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
-      </c>
-      <c r="D43" s="3"/>
-      <c r="E43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" t="s">
-        <v>56</v>
+        <v>100</v>
+      </c>
+      <c r="D43">
+        <v>4740</v>
+      </c>
+      <c r="E43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" t="s">
+        <v>7</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>152.06628499999999</v>
+      </c>
+      <c r="B44">
+        <v>-28.262926000212399</v>
       </c>
       <c r="C44" t="s">
-        <v>95</v>
-      </c>
-      <c r="D44" s="3"/>
-      <c r="E44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" t="s">
-        <v>57</v>
+        <v>100</v>
+      </c>
+      <c r="D44">
+        <v>4370</v>
+      </c>
+      <c r="E44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>145.74063100000001</v>
+      </c>
+      <c r="B45">
+        <v>-17.022808000471102</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
-      </c>
-      <c r="D45" s="3"/>
-      <c r="E45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" t="s">
-        <v>58</v>
+        <v>100</v>
+      </c>
+      <c r="D45">
+        <v>4869</v>
+      </c>
+      <c r="E45" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>150.70603800000001</v>
+      </c>
+      <c r="B46">
+        <v>-23.033566000319802</v>
       </c>
       <c r="C46" t="s">
-        <v>95</v>
-      </c>
-      <c r="D46" s="3"/>
-      <c r="E46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" t="s">
-        <v>59</v>
+        <v>100</v>
+      </c>
+      <c r="D46">
+        <v>4703</v>
+      </c>
+      <c r="E46" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>145.325862</v>
+      </c>
+      <c r="B47">
+        <v>-16.612132000482401</v>
       </c>
       <c r="C47" t="s">
-        <v>95</v>
-      </c>
-      <c r="D47" s="3"/>
-      <c r="E47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" t="s">
-        <v>60</v>
+        <v>100</v>
+      </c>
+      <c r="D47">
+        <v>4871</v>
+      </c>
+      <c r="E47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>152.681423</v>
+      </c>
+      <c r="B48">
+        <v>-26.645915000242901</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
-      </c>
-      <c r="D48" s="3"/>
-      <c r="E48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>4</v>
-      </c>
-      <c r="B49" t="s">
-        <v>61</v>
+        <v>100</v>
+      </c>
+      <c r="D48">
+        <v>4552</v>
+      </c>
+      <c r="E48" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>149.157318</v>
+      </c>
+      <c r="B49">
+        <v>-21.3759370003588</v>
       </c>
       <c r="C49" t="s">
-        <v>95</v>
-      </c>
-      <c r="D49" s="3"/>
-      <c r="E49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>62</v>
+        <v>100</v>
+      </c>
+      <c r="D49">
+        <v>4737</v>
+      </c>
+      <c r="E49" t="s">
+        <v>101</v>
+      </c>
+      <c r="F49" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>152.99049400000001</v>
+      </c>
+      <c r="B50">
+        <v>-27.994687000217301</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
-      </c>
-      <c r="D50" s="3"/>
-      <c r="E50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>63</v>
+        <v>100</v>
+      </c>
+      <c r="D50">
+        <v>4285</v>
+      </c>
+      <c r="E50" t="s">
+        <v>101</v>
+      </c>
+      <c r="F50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>152.19548700000001</v>
+      </c>
+      <c r="B51">
+        <v>-24.987928000276799</v>
       </c>
       <c r="C51" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" s="3"/>
-      <c r="E51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>64</v>
+        <v>100</v>
+      </c>
+      <c r="D51">
+        <v>4670</v>
+      </c>
+      <c r="E51" t="s">
+        <v>101</v>
+      </c>
+      <c r="F51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>145.90499</v>
+      </c>
+      <c r="B52">
+        <v>-17.208233000465999</v>
       </c>
       <c r="C52" t="s">
-        <v>95</v>
-      </c>
-      <c r="D52" s="3"/>
-      <c r="E52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>65</v>
+        <v>100</v>
+      </c>
+      <c r="D52">
+        <v>4871</v>
+      </c>
+      <c r="E52" t="s">
+        <v>101</v>
+      </c>
+      <c r="F52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>153.14320000000001</v>
+      </c>
+      <c r="B53">
+        <v>-27.616110000224399</v>
       </c>
       <c r="C53" t="s">
-        <v>95</v>
-      </c>
-      <c r="D53" s="3"/>
-      <c r="E53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>66</v>
+        <v>100</v>
+      </c>
+      <c r="D53">
+        <v>4127</v>
+      </c>
+      <c r="E53" t="s">
+        <v>101</v>
+      </c>
+      <c r="F53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>152.038623</v>
+      </c>
+      <c r="B54">
+        <v>-26.039296000255099</v>
       </c>
       <c r="C54" t="s">
-        <v>95</v>
-      </c>
-      <c r="D54" s="3"/>
-      <c r="E54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>67</v>
+        <v>100</v>
+      </c>
+      <c r="D54">
+        <v>4601</v>
+      </c>
+      <c r="E54" t="s">
+        <v>101</v>
+      </c>
+      <c r="F54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>153.23896999999999</v>
+      </c>
+      <c r="B55">
+        <v>-27.681581000223101</v>
       </c>
       <c r="C55" t="s">
-        <v>95</v>
-      </c>
-      <c r="D55" s="3"/>
-      <c r="E55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>68</v>
+        <v>100</v>
+      </c>
+      <c r="D55">
+        <v>4130</v>
+      </c>
+      <c r="E55" t="s">
+        <v>101</v>
+      </c>
+      <c r="F55" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>152.724389</v>
+      </c>
+      <c r="B56">
+        <v>-26.734515000241299</v>
       </c>
       <c r="C56" t="s">
-        <v>95</v>
-      </c>
-      <c r="D56" s="3"/>
-      <c r="E56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>69</v>
+        <v>100</v>
+      </c>
+      <c r="D56">
+        <v>4552</v>
+      </c>
+      <c r="E56" t="s">
+        <v>101</v>
+      </c>
+      <c r="F56" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>152.912609</v>
+      </c>
+      <c r="B57">
+        <v>-27.154092000233099</v>
       </c>
       <c r="C57" t="s">
-        <v>95</v>
-      </c>
-      <c r="D57" s="3"/>
-      <c r="E57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>70</v>
+        <v>100</v>
+      </c>
+      <c r="D57">
+        <v>4506</v>
+      </c>
+      <c r="E57" t="s">
+        <v>101</v>
+      </c>
+      <c r="F57" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>152.212703</v>
+      </c>
+      <c r="B58">
+        <v>-27.858089000219799</v>
       </c>
       <c r="C58" t="s">
-        <v>95</v>
-      </c>
-      <c r="D58" s="3"/>
-      <c r="E58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>4</v>
-      </c>
-      <c r="B59" t="s">
-        <v>71</v>
+        <v>100</v>
+      </c>
+      <c r="D58">
+        <v>4343</v>
+      </c>
+      <c r="E58" t="s">
+        <v>101</v>
+      </c>
+      <c r="F58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>153.053023</v>
+      </c>
+      <c r="B59">
+        <v>-27.356217000229201</v>
       </c>
       <c r="C59" t="s">
-        <v>95</v>
-      </c>
-      <c r="D59" s="3"/>
-      <c r="E59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>4</v>
-      </c>
-      <c r="B60" t="s">
-        <v>72</v>
+        <v>100</v>
+      </c>
+      <c r="D59">
+        <v>4034</v>
+      </c>
+      <c r="E59" t="s">
+        <v>101</v>
+      </c>
+      <c r="F59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>152.956988</v>
+      </c>
+      <c r="B60">
+        <v>-27.0260850002356</v>
       </c>
       <c r="C60" t="s">
-        <v>95</v>
-      </c>
-      <c r="D60" s="3"/>
-      <c r="E60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>4</v>
-      </c>
-      <c r="B61" t="s">
-        <v>73</v>
+        <v>100</v>
+      </c>
+      <c r="D60">
+        <v>4516</v>
+      </c>
+      <c r="E60" t="s">
+        <v>101</v>
+      </c>
+      <c r="F60" t="s">
+        <v>7</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>152.96185500000001</v>
+      </c>
+      <c r="B61">
+        <v>-26.648363000242899</v>
       </c>
       <c r="C61" t="s">
-        <v>95</v>
-      </c>
-      <c r="D61" s="3"/>
-      <c r="E61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>4</v>
-      </c>
-      <c r="B62" t="s">
-        <v>74</v>
+        <v>100</v>
+      </c>
+      <c r="D61">
+        <v>4559</v>
+      </c>
+      <c r="E61" t="s">
+        <v>101</v>
+      </c>
+      <c r="F61" t="s">
+        <v>7</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>146.092049</v>
+      </c>
+      <c r="B62">
+        <v>-17.876942000448</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
-      </c>
-      <c r="D62" s="3"/>
-      <c r="E62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" t="s">
-        <v>75</v>
+        <v>100</v>
+      </c>
+      <c r="D62">
+        <v>4852</v>
+      </c>
+      <c r="E62" t="s">
+        <v>101</v>
+      </c>
+      <c r="F62" t="s">
+        <v>7</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>151.93415999999999</v>
+      </c>
+      <c r="B63">
+        <v>-28.578292000206702</v>
       </c>
       <c r="C63" t="s">
-        <v>95</v>
-      </c>
-      <c r="D63" s="3"/>
-      <c r="E63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>4</v>
-      </c>
-      <c r="B64" t="s">
-        <v>76</v>
+        <v>100</v>
+      </c>
+      <c r="D63">
+        <v>4377</v>
+      </c>
+      <c r="E63" t="s">
+        <v>101</v>
+      </c>
+      <c r="F63" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>152.37705199999999</v>
+      </c>
+      <c r="B64">
+        <v>-24.874515000279199</v>
       </c>
       <c r="C64" t="s">
-        <v>95</v>
-      </c>
-      <c r="D64" s="3"/>
-      <c r="E64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>4</v>
-      </c>
-      <c r="B65" t="s">
-        <v>77</v>
+        <v>100</v>
+      </c>
+      <c r="D64">
+        <v>4670</v>
+      </c>
+      <c r="E64" t="s">
+        <v>101</v>
+      </c>
+      <c r="F64" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>152.81597500000001</v>
+      </c>
+      <c r="B65">
+        <v>-26.848657000239001</v>
       </c>
       <c r="C65" t="s">
-        <v>95</v>
-      </c>
-      <c r="D65" s="3"/>
-      <c r="E65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>4</v>
-      </c>
-      <c r="B66" t="s">
-        <v>78</v>
+        <v>100</v>
+      </c>
+      <c r="D65">
+        <v>4514</v>
+      </c>
+      <c r="E65" t="s">
+        <v>101</v>
+      </c>
+      <c r="F65" t="s">
+        <v>7</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>150.393325</v>
+      </c>
+      <c r="B66">
+        <v>-23.673240000305402</v>
       </c>
       <c r="C66" t="s">
-        <v>95</v>
-      </c>
-      <c r="D66" s="3"/>
-      <c r="E66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>4</v>
-      </c>
-      <c r="B67" t="s">
-        <v>79</v>
+        <v>100</v>
+      </c>
+      <c r="D66">
+        <v>4714</v>
+      </c>
+      <c r="E66" t="s">
+        <v>101</v>
+      </c>
+      <c r="F66" t="s">
+        <v>7</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>152.97665799999999</v>
+      </c>
+      <c r="B67">
+        <v>-27.171754000232799</v>
       </c>
       <c r="C67" t="s">
-        <v>95</v>
-      </c>
-      <c r="D67" s="3"/>
-      <c r="E67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>4</v>
-      </c>
-      <c r="B68" t="s">
-        <v>80</v>
+        <v>100</v>
+      </c>
+      <c r="D67">
+        <v>4505</v>
+      </c>
+      <c r="E67" t="s">
+        <v>101</v>
+      </c>
+      <c r="F67" t="s">
+        <v>7</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>152.289558</v>
+      </c>
+      <c r="B68">
+        <v>-26.0818920002542</v>
       </c>
       <c r="C68" t="s">
-        <v>95</v>
-      </c>
-      <c r="D68" s="3"/>
-      <c r="E68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>4</v>
-      </c>
-      <c r="B69" t="s">
-        <v>81</v>
+        <v>100</v>
+      </c>
+      <c r="D68">
+        <v>4600</v>
+      </c>
+      <c r="E68" t="s">
+        <v>101</v>
+      </c>
+      <c r="F68" t="s">
+        <v>7</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>152.10591700000001</v>
+      </c>
+      <c r="B69">
+        <v>-28.032273000216598</v>
       </c>
       <c r="C69" t="s">
-        <v>95</v>
-      </c>
-      <c r="D69" s="3"/>
-      <c r="E69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>4</v>
-      </c>
-      <c r="B70" t="s">
-        <v>82</v>
+        <v>100</v>
+      </c>
+      <c r="D69">
+        <v>4362</v>
+      </c>
+      <c r="E69" t="s">
+        <v>101</v>
+      </c>
+      <c r="F69" t="s">
+        <v>7</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>152.14037099999999</v>
+      </c>
+      <c r="B70">
+        <v>-28.115408000215101</v>
       </c>
       <c r="C70" t="s">
-        <v>95</v>
-      </c>
-      <c r="D70" s="3"/>
-      <c r="E70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>4</v>
-      </c>
-      <c r="B71" t="s">
-        <v>83</v>
+        <v>100</v>
+      </c>
+      <c r="D70">
+        <v>4370</v>
+      </c>
+      <c r="E70" t="s">
+        <v>101</v>
+      </c>
+      <c r="F70" t="s">
+        <v>7</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>151.73176000000001</v>
+      </c>
+      <c r="B71">
+        <v>-28.705545000204499</v>
       </c>
       <c r="C71" t="s">
-        <v>95</v>
-      </c>
-      <c r="D71" s="3"/>
-      <c r="E71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>4</v>
-      </c>
-      <c r="B72" t="s">
-        <v>84</v>
+        <v>100</v>
+      </c>
+      <c r="D71">
+        <v>4380</v>
+      </c>
+      <c r="E71" t="s">
+        <v>101</v>
+      </c>
+      <c r="F71" t="s">
+        <v>7</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>153.21440000000001</v>
+      </c>
+      <c r="B72">
+        <v>-27.674522000223199</v>
       </c>
       <c r="C72" t="s">
-        <v>95</v>
-      </c>
-      <c r="D72" s="3"/>
-      <c r="E72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>4</v>
-      </c>
-      <c r="B73" t="s">
-        <v>85</v>
+        <v>100</v>
+      </c>
+      <c r="D72">
+        <v>4130</v>
+      </c>
+      <c r="E72" t="s">
+        <v>101</v>
+      </c>
+      <c r="F72" t="s">
+        <v>7</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>152.223186</v>
+      </c>
+      <c r="B73">
+        <v>-25.192344000272499</v>
       </c>
       <c r="C73" t="s">
-        <v>95</v>
-      </c>
-      <c r="D73" s="3"/>
-      <c r="E73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>4</v>
-      </c>
-      <c r="B74" t="s">
-        <v>86</v>
+        <v>100</v>
+      </c>
+      <c r="D73">
+        <v>4660</v>
+      </c>
+      <c r="E73" t="s">
+        <v>101</v>
+      </c>
+      <c r="F73" t="s">
+        <v>7</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>146.94357600000001</v>
+      </c>
+      <c r="B74">
+        <v>-19.6117700004027</v>
       </c>
       <c r="C74" t="s">
-        <v>95</v>
-      </c>
-      <c r="D74" s="3"/>
-      <c r="E74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>4</v>
-      </c>
-      <c r="B75" t="s">
-        <v>87</v>
+        <v>100</v>
+      </c>
+      <c r="D74">
+        <v>4816</v>
+      </c>
+      <c r="E74" t="s">
+        <v>101</v>
+      </c>
+      <c r="F74" t="s">
+        <v>7</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>146.13551699999999</v>
+      </c>
+      <c r="B75">
+        <v>-20.145193000389199</v>
       </c>
       <c r="C75" t="s">
-        <v>95</v>
-      </c>
-      <c r="D75" s="3"/>
-      <c r="E75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>4</v>
-      </c>
-      <c r="B76" t="s">
-        <v>88</v>
+        <v>100</v>
+      </c>
+      <c r="D75">
+        <v>4820</v>
+      </c>
+      <c r="E75" t="s">
+        <v>101</v>
+      </c>
+      <c r="F75" t="s">
+        <v>7</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>150.50894199999999</v>
+      </c>
+      <c r="B76">
+        <v>-23.407007000311399</v>
       </c>
       <c r="C76" t="s">
-        <v>95</v>
-      </c>
-      <c r="D76" s="3"/>
-      <c r="E76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>4</v>
-      </c>
-      <c r="B77" t="s">
-        <v>89</v>
+        <v>100</v>
+      </c>
+      <c r="D76">
+        <v>4700</v>
+      </c>
+      <c r="E76" t="s">
+        <v>101</v>
+      </c>
+      <c r="F76" t="s">
+        <v>7</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>147.14408900000001</v>
+      </c>
+      <c r="B77">
+        <v>-19.616306000402599</v>
       </c>
       <c r="C77" t="s">
-        <v>95</v>
-      </c>
-      <c r="D77" s="3"/>
-      <c r="E77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>4</v>
-      </c>
-      <c r="B78" t="s">
-        <v>90</v>
+        <v>100</v>
+      </c>
+      <c r="D77">
+        <v>4809</v>
+      </c>
+      <c r="E77" t="s">
+        <v>101</v>
+      </c>
+      <c r="F77" t="s">
+        <v>7</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>147.03102100000001</v>
+      </c>
+      <c r="B78">
+        <v>-19.497065000405598</v>
       </c>
       <c r="C78" t="s">
-        <v>95</v>
-      </c>
-      <c r="D78" s="3"/>
-      <c r="E78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>4</v>
-      </c>
-      <c r="B79" t="s">
-        <v>91</v>
+        <v>100</v>
+      </c>
+      <c r="D78">
+        <v>4809</v>
+      </c>
+      <c r="E78" t="s">
+        <v>101</v>
+      </c>
+      <c r="F78" t="s">
+        <v>7</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>151.11836</v>
+      </c>
+      <c r="B79">
+        <v>-24.8704550002793</v>
       </c>
       <c r="C79" t="s">
-        <v>95</v>
-      </c>
-      <c r="D79" s="3"/>
-      <c r="E79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-    </row>
-    <row r="81" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-    </row>
-    <row r="82" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-    </row>
-    <row r="83" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-    </row>
-    <row r="84" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-    </row>
-    <row r="85" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-    </row>
-    <row r="86" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-    </row>
-    <row r="87" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-    </row>
-    <row r="88" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-    </row>
-    <row r="89" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-    </row>
-    <row r="90" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-    </row>
-    <row r="91" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-    </row>
-    <row r="92" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-    </row>
-    <row r="93" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-    </row>
-    <row r="94" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-    </row>
-    <row r="95" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-    </row>
-    <row r="96" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-    </row>
-    <row r="97" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-    </row>
-    <row r="98" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-    </row>
-    <row r="99" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-    </row>
-    <row r="100" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-    </row>
-    <row r="101" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
-    </row>
-    <row r="102" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
-    </row>
-    <row r="103" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-    </row>
-    <row r="104" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
-    </row>
-    <row r="105" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
-    </row>
-    <row r="106" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-    </row>
-    <row r="107" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D107" s="3"/>
-      <c r="E107" s="3"/>
-    </row>
-    <row r="108" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
-    </row>
-    <row r="109" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-    </row>
-    <row r="110" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-    </row>
-    <row r="111" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-    </row>
-    <row r="112" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
-    </row>
-    <row r="113" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
-    </row>
-    <row r="114" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-    </row>
-    <row r="115" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
-    </row>
-    <row r="116" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-    </row>
-    <row r="117" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-    </row>
-    <row r="118" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-    </row>
-    <row r="119" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-    </row>
-    <row r="120" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
-    </row>
-    <row r="121" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D121" s="3"/>
-      <c r="E121" s="3"/>
-    </row>
-    <row r="122" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D122" s="3"/>
-      <c r="E122" s="3"/>
-    </row>
-    <row r="123" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D123" s="3"/>
-      <c r="E123" s="3"/>
-    </row>
-    <row r="124" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D124" s="3"/>
-      <c r="E124" s="3"/>
-    </row>
-    <row r="125" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D125" s="3"/>
-      <c r="E125" s="3"/>
-    </row>
-    <row r="126" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D126" s="3"/>
-      <c r="E126" s="3"/>
-    </row>
-    <row r="127" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D127" s="3"/>
-      <c r="E127" s="3"/>
-    </row>
-    <row r="128" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D128" s="3"/>
-      <c r="E128" s="3"/>
-    </row>
-    <row r="129" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
-    </row>
-    <row r="130" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D130" s="3"/>
-      <c r="E130" s="3"/>
-    </row>
-    <row r="131" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D131" s="3"/>
-      <c r="E131" s="3"/>
-    </row>
-    <row r="132" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D132" s="3"/>
-      <c r="E132" s="3"/>
-    </row>
-    <row r="133" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D133" s="3"/>
-      <c r="E133" s="3"/>
-    </row>
-    <row r="134" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D134" s="3"/>
-      <c r="E134" s="3"/>
-    </row>
-    <row r="135" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D135" s="3"/>
-      <c r="E135" s="3"/>
-    </row>
-    <row r="136" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D136" s="3"/>
-      <c r="E136" s="3"/>
-    </row>
-    <row r="137" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D137" s="3"/>
-      <c r="E137" s="3"/>
-    </row>
-    <row r="138" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D138" s="3"/>
-      <c r="E138" s="3"/>
-    </row>
-    <row r="139" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D139" s="3"/>
-      <c r="E139" s="3"/>
-    </row>
-    <row r="140" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D140" s="3"/>
-      <c r="E140" s="3"/>
-    </row>
-    <row r="141" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D141" s="3"/>
-      <c r="E141" s="3"/>
-    </row>
-    <row r="142" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D142" s="3"/>
-      <c r="E142" s="3"/>
-    </row>
-    <row r="143" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D143" s="3"/>
-      <c r="E143" s="3"/>
-    </row>
-    <row r="144" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D144" s="3"/>
-      <c r="E144" s="3"/>
-    </row>
-    <row r="145" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D145" s="3"/>
-      <c r="E145" s="3"/>
-    </row>
-    <row r="146" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D146" s="3"/>
-      <c r="E146" s="3"/>
-    </row>
-    <row r="147" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D147" s="3"/>
-      <c r="E147" s="3"/>
-    </row>
-    <row r="148" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D148" s="3"/>
-      <c r="E148" s="3"/>
-    </row>
-    <row r="149" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D149" s="3"/>
-      <c r="E149" s="3"/>
-    </row>
-    <row r="150" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D150" s="3"/>
-      <c r="E150" s="3"/>
-    </row>
-    <row r="151" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D151" s="3"/>
-      <c r="E151" s="3"/>
-    </row>
-    <row r="152" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D152" s="3"/>
-      <c r="E152" s="3"/>
-    </row>
-    <row r="153" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D153" s="3"/>
-      <c r="E153" s="3"/>
-    </row>
-    <row r="154" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D154" s="3"/>
-      <c r="E154" s="3"/>
-    </row>
-    <row r="155" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D155" s="3"/>
-      <c r="E155" s="3"/>
-    </row>
-    <row r="156" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D156" s="3"/>
-      <c r="E156" s="3"/>
-    </row>
-    <row r="157" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D157" s="3"/>
-      <c r="E157" s="3"/>
-    </row>
-    <row r="158" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D158" s="3"/>
-      <c r="E158" s="3"/>
-    </row>
-    <row r="159" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D159" s="3"/>
-      <c r="E159" s="3"/>
-    </row>
-    <row r="160" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D160" s="3"/>
-      <c r="E160" s="3"/>
-    </row>
-    <row r="161" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D161" s="3"/>
-      <c r="E161" s="3"/>
-    </row>
-    <row r="162" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D162" s="3"/>
-      <c r="E162" s="3"/>
-    </row>
-    <row r="163" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D163" s="3"/>
-      <c r="E163" s="3"/>
-    </row>
-    <row r="164" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D164" s="3"/>
-      <c r="E164" s="3"/>
-    </row>
-    <row r="165" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D165" s="3"/>
-      <c r="E165" s="3"/>
-    </row>
-    <row r="166" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D166" s="3"/>
-      <c r="E166" s="3"/>
-    </row>
-    <row r="167" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D167" s="3"/>
-      <c r="E167" s="3"/>
-    </row>
-    <row r="168" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D168" s="3"/>
-      <c r="E168" s="3"/>
-    </row>
-    <row r="169" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D169" s="3"/>
-      <c r="E169" s="3"/>
-    </row>
-    <row r="170" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D170" s="3"/>
-      <c r="E170" s="3"/>
-    </row>
-    <row r="171" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D171" s="3"/>
-      <c r="E171" s="3"/>
-    </row>
-    <row r="172" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D172" s="3"/>
-      <c r="E172" s="3"/>
-    </row>
-    <row r="173" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D173" s="3"/>
-      <c r="E173" s="3"/>
-    </row>
-    <row r="174" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D174" s="3"/>
-      <c r="E174" s="3"/>
-    </row>
-    <row r="175" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D175" s="3"/>
-      <c r="E175" s="3"/>
-    </row>
-    <row r="176" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D176" s="3"/>
-      <c r="E176" s="3"/>
-    </row>
-    <row r="177" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D177" s="3"/>
-      <c r="E177" s="3"/>
-    </row>
-    <row r="178" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D178" s="3"/>
-      <c r="E178" s="3"/>
-    </row>
-    <row r="179" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D179" s="3"/>
-      <c r="E179" s="3"/>
-    </row>
-    <row r="180" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D180" s="3"/>
-      <c r="E180" s="3"/>
-    </row>
-    <row r="181" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D181" s="3"/>
-      <c r="E181" s="3"/>
-    </row>
-    <row r="182" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D182" s="3"/>
-      <c r="E182" s="3"/>
-    </row>
-    <row r="183" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D183" s="3"/>
-      <c r="E183" s="3"/>
-    </row>
-    <row r="184" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D184" s="3"/>
-      <c r="E184" s="3"/>
-    </row>
-    <row r="185" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D185" s="3"/>
-      <c r="E185" s="3"/>
-    </row>
-    <row r="186" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D186" s="3"/>
-      <c r="E186" s="3"/>
-    </row>
-    <row r="187" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D187" s="3"/>
-      <c r="E187" s="3"/>
-    </row>
-    <row r="188" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D188" s="3"/>
-      <c r="E188" s="3"/>
-    </row>
-    <row r="189" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D189" s="3"/>
-      <c r="E189" s="3"/>
-    </row>
-    <row r="190" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D190" s="3"/>
-      <c r="E190" s="3"/>
-    </row>
-    <row r="191" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D191" s="3"/>
-      <c r="E191" s="3"/>
-    </row>
-    <row r="192" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D192" s="3"/>
-      <c r="E192" s="3"/>
-    </row>
-    <row r="193" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D193" s="3"/>
-      <c r="E193" s="3"/>
-    </row>
-    <row r="194" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D194" s="3"/>
-      <c r="E194" s="3"/>
-    </row>
-    <row r="195" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D195" s="3"/>
-      <c r="E195" s="3"/>
-    </row>
-    <row r="196" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D196" s="3"/>
-      <c r="E196" s="3"/>
-    </row>
-    <row r="197" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D197" s="3"/>
-      <c r="E197" s="3"/>
-    </row>
-    <row r="198" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D198" s="3"/>
-      <c r="E198" s="3"/>
-    </row>
-    <row r="199" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D199" s="3"/>
-      <c r="E199" s="3"/>
-    </row>
-    <row r="200" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D200" s="3"/>
-      <c r="E200" s="3"/>
-    </row>
-    <row r="201" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D201" s="3"/>
-      <c r="E201" s="3"/>
-    </row>
-    <row r="202" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D202" s="3"/>
-      <c r="E202" s="3"/>
-    </row>
-    <row r="203" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D203" s="3"/>
-      <c r="E203" s="3"/>
-    </row>
-    <row r="204" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D204" s="3"/>
-      <c r="E204" s="3"/>
-    </row>
-    <row r="205" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D205" s="3"/>
-      <c r="E205" s="3"/>
-    </row>
-    <row r="206" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D206" s="3"/>
-      <c r="E206" s="3"/>
-    </row>
-    <row r="207" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D207" s="3"/>
-      <c r="E207" s="3"/>
-    </row>
-    <row r="208" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D208" s="3"/>
-      <c r="E208" s="3"/>
-    </row>
-    <row r="209" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D209" s="3"/>
-      <c r="E209" s="3"/>
-    </row>
-    <row r="210" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D210" s="3"/>
-      <c r="E210" s="3"/>
-    </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D211" s="3"/>
-      <c r="E211" s="3"/>
-    </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D212" s="3"/>
-      <c r="E212" s="3"/>
-    </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D213" s="3"/>
-      <c r="E213" s="3"/>
-    </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D214" s="3"/>
-      <c r="E214" s="3"/>
-    </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D215" s="3"/>
-      <c r="E215" s="3"/>
-    </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D216" s="3"/>
-      <c r="E216" s="3"/>
-    </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D217" s="3"/>
-      <c r="E217" s="3"/>
-    </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D218" s="3"/>
-      <c r="E218" s="3"/>
-    </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D219" s="3"/>
-      <c r="E219" s="3"/>
-    </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D220" s="3"/>
-      <c r="E220" s="3"/>
-    </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D221" s="3"/>
-      <c r="E221" s="3"/>
-    </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D222" s="3"/>
-      <c r="E222" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="D79">
+        <v>4630</v>
+      </c>
+      <c r="E79" t="s">
+        <v>101</v>
+      </c>
+      <c r="F79" t="s">
+        <v>7</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>152.03702999999999</v>
+      </c>
+      <c r="B80">
+        <v>-24.946310000277698</v>
+      </c>
+      <c r="C80" t="s">
+        <v>100</v>
+      </c>
+      <c r="D80">
+        <v>4671</v>
+      </c>
+      <c r="E80" t="s">
+        <v>101</v>
+      </c>
+      <c r="F80" t="s">
+        <v>7</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>145.52409700000001</v>
+      </c>
+      <c r="B81">
+        <v>-17.215188000465801</v>
+      </c>
+      <c r="C81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D81">
+        <v>4872</v>
+      </c>
+      <c r="E81" t="s">
+        <v>101</v>
+      </c>
+      <c r="F81" t="s">
+        <v>7</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>148.96055100000001</v>
+      </c>
+      <c r="B82">
+        <v>-21.0073250003678</v>
+      </c>
+      <c r="C82" t="s">
+        <v>100</v>
+      </c>
+      <c r="D82">
+        <v>4740</v>
+      </c>
+      <c r="E82" t="s">
+        <v>101</v>
+      </c>
+      <c r="F82" t="s">
+        <v>7</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>152.83248699999999</v>
+      </c>
+      <c r="B83">
+        <v>-25.282805000270599</v>
+      </c>
+      <c r="C83" t="s">
+        <v>100</v>
+      </c>
+      <c r="D83">
+        <v>4655</v>
+      </c>
+      <c r="E83" t="s">
+        <v>101</v>
+      </c>
+      <c r="F83" t="s">
+        <v>7</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>148.238088</v>
+      </c>
+      <c r="B84">
+        <v>-20.061264000391301</v>
+      </c>
+      <c r="C84" t="s">
+        <v>100</v>
+      </c>
+      <c r="D84">
+        <v>4805</v>
+      </c>
+      <c r="E84" t="s">
+        <v>101</v>
+      </c>
+      <c r="F84" t="s">
+        <v>7</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>145.056701</v>
+      </c>
+      <c r="B85">
+        <v>-17.1914130004665</v>
+      </c>
+      <c r="C85" t="s">
+        <v>100</v>
+      </c>
+      <c r="D85">
+        <v>4872</v>
+      </c>
+      <c r="E85" t="s">
+        <v>101</v>
+      </c>
+      <c r="F85" t="s">
+        <v>7</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>152.651715</v>
+      </c>
+      <c r="B86">
+        <v>-26.352001000248801</v>
+      </c>
+      <c r="C86" t="s">
+        <v>100</v>
+      </c>
+      <c r="D86">
+        <v>4570</v>
+      </c>
+      <c r="E86" t="s">
+        <v>101</v>
+      </c>
+      <c r="F86" t="s">
+        <v>7</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>153.04044099999999</v>
+      </c>
+      <c r="B87">
+        <v>-28.154104000214399</v>
+      </c>
+      <c r="C87" t="s">
+        <v>100</v>
+      </c>
+      <c r="D87">
+        <v>4285</v>
+      </c>
+      <c r="E87" t="s">
+        <v>101</v>
+      </c>
+      <c r="F87" t="s">
+        <v>7</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>148.03983299999999</v>
+      </c>
+      <c r="B88">
+        <v>-22.006085000343798</v>
+      </c>
+      <c r="C88" t="s">
+        <v>100</v>
+      </c>
+      <c r="D88">
+        <v>4744</v>
+      </c>
+      <c r="E88" t="s">
+        <v>101</v>
+      </c>
+      <c r="F88" t="s">
+        <v>7</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>151.25914399999999</v>
+      </c>
+      <c r="B89">
+        <v>-25.839397000259101</v>
+      </c>
+      <c r="C89" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89">
+        <v>4626</v>
+      </c>
+      <c r="E89" t="s">
+        <v>101</v>
+      </c>
+      <c r="F89" t="s">
+        <v>7</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>145.93233799999999</v>
+      </c>
+      <c r="B90">
+        <v>-17.934707000446501</v>
+      </c>
+      <c r="C90" t="s">
+        <v>100</v>
+      </c>
+      <c r="D90">
+        <v>4854</v>
+      </c>
+      <c r="E90" t="s">
+        <v>101</v>
+      </c>
+      <c r="F90" t="s">
+        <v>7</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>152.01148900000001</v>
+      </c>
+      <c r="B91">
+        <v>-28.277086000212101</v>
+      </c>
+      <c r="C91" t="s">
+        <v>100</v>
+      </c>
+      <c r="D91">
+        <v>4370</v>
+      </c>
+      <c r="E91" t="s">
+        <v>101</v>
+      </c>
+      <c r="F91" t="s">
+        <v>7</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>151.807738</v>
+      </c>
+      <c r="B92">
+        <v>-27.834856000220199</v>
+      </c>
+      <c r="C92" t="s">
+        <v>100</v>
+      </c>
+      <c r="D92">
+        <v>4358</v>
+      </c>
+      <c r="E92" t="s">
+        <v>101</v>
+      </c>
+      <c r="F92" t="s">
+        <v>7</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>152.36685299999999</v>
+      </c>
+      <c r="B93">
+        <v>-26.944171000237201</v>
+      </c>
+      <c r="C93" t="s">
+        <v>100</v>
+      </c>
+      <c r="D93">
+        <v>4306</v>
+      </c>
+      <c r="E93" t="s">
+        <v>101</v>
+      </c>
+      <c r="F93" t="s">
+        <v>7</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>152.377995</v>
+      </c>
+      <c r="B94">
+        <v>-26.936936000237299</v>
+      </c>
+      <c r="C94" t="s">
+        <v>100</v>
+      </c>
+      <c r="D94">
+        <v>4306</v>
+      </c>
+      <c r="E94" t="s">
+        <v>101</v>
+      </c>
+      <c r="F94" t="s">
+        <v>7</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>152.457391</v>
+      </c>
+      <c r="B95">
+        <v>-26.934192000237299</v>
+      </c>
+      <c r="C95" t="s">
+        <v>100</v>
+      </c>
+      <c r="D95">
+        <v>4306</v>
+      </c>
+      <c r="E95" t="s">
+        <v>101</v>
+      </c>
+      <c r="F95" t="s">
+        <v>7</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>152.77750599999999</v>
+      </c>
+      <c r="B96">
+        <v>-26.8872880002382</v>
+      </c>
+      <c r="C96" t="s">
+        <v>100</v>
+      </c>
+      <c r="D96">
+        <v>4514</v>
+      </c>
+      <c r="E96" t="s">
+        <v>101</v>
+      </c>
+      <c r="F96" t="s">
+        <v>7</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>152.70520500000001</v>
+      </c>
+      <c r="B97">
+        <v>-26.9438720002371</v>
+      </c>
+      <c r="C97" t="s">
+        <v>100</v>
+      </c>
+      <c r="D97">
+        <v>4514</v>
+      </c>
+      <c r="E97" t="s">
+        <v>101</v>
+      </c>
+      <c r="F97" t="s">
+        <v>7</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>151.67125100000001</v>
+      </c>
+      <c r="B98">
+        <v>-27.722798000222301</v>
+      </c>
+      <c r="C98" t="s">
+        <v>100</v>
+      </c>
+      <c r="D98">
+        <v>4356</v>
+      </c>
+      <c r="E98" t="s">
+        <v>101</v>
+      </c>
+      <c r="F98" t="s">
+        <v>7</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>151.37503000000001</v>
+      </c>
+      <c r="B99">
+        <v>-28.013757000216899</v>
+      </c>
+      <c r="C99" t="s">
+        <v>100</v>
+      </c>
+      <c r="D99">
+        <v>4357</v>
+      </c>
+      <c r="E99" t="s">
+        <v>101</v>
+      </c>
+      <c r="F99" t="s">
+        <v>7</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>145.97720899999999</v>
+      </c>
+      <c r="B100">
+        <v>-17.578140000455999</v>
+      </c>
+      <c r="C100" t="s">
+        <v>100</v>
+      </c>
+      <c r="D100">
+        <v>4860</v>
+      </c>
+      <c r="E100" t="s">
+        <v>101</v>
+      </c>
+      <c r="F100" t="s">
+        <v>7</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>151.67320599999999</v>
+      </c>
+      <c r="B101">
+        <v>-27.777369000221299</v>
+      </c>
+      <c r="C101" t="s">
+        <v>100</v>
+      </c>
+      <c r="D101">
+        <v>4358</v>
+      </c>
+      <c r="E101" t="s">
+        <v>12</v>
+      </c>
+      <c r="F101" t="s">
+        <v>7</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>152.06246300000001</v>
+      </c>
+      <c r="B102">
+        <v>-28.247982000212701</v>
+      </c>
+      <c r="C102" t="s">
+        <v>100</v>
+      </c>
+      <c r="D102">
+        <v>4370</v>
+      </c>
+      <c r="E102" t="s">
+        <v>12</v>
+      </c>
+      <c r="F102" t="s">
+        <v>7</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>153.26206500000001</v>
+      </c>
+      <c r="B103">
+        <v>-27.620805000224198</v>
+      </c>
+      <c r="C103" t="s">
+        <v>100</v>
+      </c>
+      <c r="D103">
+        <v>4165</v>
+      </c>
+      <c r="E103" t="s">
+        <v>12</v>
+      </c>
+      <c r="F103" t="s">
+        <v>7</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>151.33095399999999</v>
+      </c>
+      <c r="B104">
+        <v>-27.84945100022</v>
+      </c>
+      <c r="C104" t="s">
+        <v>100</v>
+      </c>
+      <c r="D104">
+        <v>4352</v>
+      </c>
+      <c r="E104" t="s">
+        <v>12</v>
+      </c>
+      <c r="F104" t="s">
+        <v>7</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>152.95385300000001</v>
+      </c>
+      <c r="B105">
+        <v>-27.878461000219399</v>
+      </c>
+      <c r="C105" t="s">
+        <v>100</v>
+      </c>
+      <c r="D105">
+        <v>4285</v>
+      </c>
+      <c r="E105" t="s">
+        <v>12</v>
+      </c>
+      <c r="F105" t="s">
+        <v>7</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>152.86914300000001</v>
+      </c>
+      <c r="B106">
+        <v>-27.0315620002355</v>
+      </c>
+      <c r="C106" t="s">
+        <v>100</v>
+      </c>
+      <c r="D106">
+        <v>4512</v>
+      </c>
+      <c r="E106" t="s">
+        <v>12</v>
+      </c>
+      <c r="F106" t="s">
+        <v>7</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>146.710227</v>
+      </c>
+      <c r="B107">
+        <v>-19.363460000408999</v>
+      </c>
+      <c r="C107" t="s">
+        <v>100</v>
+      </c>
+      <c r="D107">
+        <v>4815</v>
+      </c>
+      <c r="E107" t="s">
+        <v>12</v>
+      </c>
+      <c r="F107" t="s">
+        <v>7</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>151.86622199999999</v>
+      </c>
+      <c r="B108">
+        <v>-27.541199000225699</v>
+      </c>
+      <c r="C108" t="s">
+        <v>100</v>
+      </c>
+      <c r="D108">
+        <v>4350</v>
+      </c>
+      <c r="E108" t="s">
+        <v>12</v>
+      </c>
+      <c r="F108" t="s">
+        <v>7</v>
+      </c>
+      <c r="G108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>152.923993</v>
+      </c>
+      <c r="B109">
+        <v>-27.610711000224399</v>
+      </c>
+      <c r="C109" t="s">
+        <v>100</v>
+      </c>
+      <c r="D109">
+        <v>4300</v>
+      </c>
+      <c r="E109" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109" t="s">
+        <v>7</v>
+      </c>
+      <c r="G109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>151.56319999999999</v>
+      </c>
+      <c r="B110">
+        <v>-27.7375640002221</v>
+      </c>
+      <c r="C110" t="s">
+        <v>100</v>
+      </c>
+      <c r="D110">
+        <v>4356</v>
+      </c>
+      <c r="E110" t="s">
+        <v>12</v>
+      </c>
+      <c r="F110" t="s">
+        <v>7</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>152.963436</v>
+      </c>
+      <c r="B111">
+        <v>-26.9750670002365</v>
+      </c>
+      <c r="C111" t="s">
+        <v>100</v>
+      </c>
+      <c r="D111">
+        <v>4517</v>
+      </c>
+      <c r="E111" t="s">
+        <v>12</v>
+      </c>
+      <c r="F111" t="s">
+        <v>7</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E222" xr:uid="{1BC8E976-27F5-4CF2-963C-1DA4DC754C80}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3769,7 +4584,7 @@
         <v>14</v>
       </c>
       <c r="C74" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>7</v>
@@ -3786,7 +4601,7 @@
         <v>15</v>
       </c>
       <c r="C75" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>7</v>
@@ -3803,7 +4618,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>7</v>
@@ -3820,7 +4635,7 @@
         <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>7</v>
@@ -3837,7 +4652,7 @@
         <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>7</v>
@@ -3854,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C79" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>7</v>
@@ -3871,7 +4686,7 @@
         <v>20</v>
       </c>
       <c r="C80" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>7</v>
@@ -3888,7 +4703,7 @@
         <v>21</v>
       </c>
       <c r="C81" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>7</v>
@@ -3905,7 +4720,7 @@
         <v>22</v>
       </c>
       <c r="C82" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>7</v>
@@ -3922,7 +4737,7 @@
         <v>23</v>
       </c>
       <c r="C83" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>7</v>
@@ -3939,7 +4754,7 @@
         <v>24</v>
       </c>
       <c r="C84" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>7</v>
@@ -3956,7 +4771,7 @@
         <v>25</v>
       </c>
       <c r="C85" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>7</v>
@@ -3973,7 +4788,7 @@
         <v>26</v>
       </c>
       <c r="C86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>7</v>
@@ -3990,7 +4805,7 @@
         <v>27</v>
       </c>
       <c r="C87" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>7</v>
@@ -4007,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="C88" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>7</v>
@@ -4024,7 +4839,7 @@
         <v>29</v>
       </c>
       <c r="C89" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>7</v>
@@ -4041,7 +4856,7 @@
         <v>30</v>
       </c>
       <c r="C90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>7</v>
@@ -4058,7 +4873,7 @@
         <v>31</v>
       </c>
       <c r="C91" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>7</v>
@@ -4075,7 +4890,7 @@
         <v>32</v>
       </c>
       <c r="C92" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>7</v>
@@ -4092,7 +4907,7 @@
         <v>33</v>
       </c>
       <c r="C93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>7</v>
@@ -4109,7 +4924,7 @@
         <v>34</v>
       </c>
       <c r="C94" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>7</v>
@@ -4126,7 +4941,7 @@
         <v>35</v>
       </c>
       <c r="C95" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>7</v>
@@ -4143,7 +4958,7 @@
         <v>36</v>
       </c>
       <c r="C96" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>7</v>
@@ -4160,7 +4975,7 @@
         <v>37</v>
       </c>
       <c r="C97" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>7</v>
@@ -4675,8 +5490,1785 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC8E976-27F5-4CF2-963C-1DA4DC754C80}">
+  <dimension ref="A1:E222"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="34.75" customWidth="1"/>
+    <col min="3" max="3" width="87.25" customWidth="1"/>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="5" max="5" width="27.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2">
+        <v>35.49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3">
+        <v>28.18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4">
+        <v>17.920000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5">
+        <v>15.77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6">
+        <v>13.93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7">
+        <v>13.87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8">
+        <v>13.09</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9">
+        <v>12.31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10">
+        <v>11.29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11">
+        <v>10.08</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13">
+        <v>8.89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16">
+        <v>6.21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27">
+        <v>2.4700000000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" t="s">
+        <v>94</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" t="s">
+        <v>94</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" t="s">
+        <v>94</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="E44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" t="s">
+        <v>94</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" s="3"/>
+      <c r="E47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="3"/>
+      <c r="E48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" t="s">
+        <v>94</v>
+      </c>
+      <c r="D49" s="3"/>
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" s="3"/>
+      <c r="E51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" t="s">
+        <v>94</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" t="s">
+        <v>94</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" t="s">
+        <v>67</v>
+      </c>
+      <c r="C55" t="s">
+        <v>94</v>
+      </c>
+      <c r="D55" s="3"/>
+      <c r="E55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" t="s">
+        <v>94</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" t="s">
+        <v>94</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" t="s">
+        <v>94</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" t="s">
+        <v>94</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" t="s">
+        <v>72</v>
+      </c>
+      <c r="C60" t="s">
+        <v>94</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62" t="s">
+        <v>94</v>
+      </c>
+      <c r="D62" s="3"/>
+      <c r="E62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" t="s">
+        <v>75</v>
+      </c>
+      <c r="C63" t="s">
+        <v>94</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" t="s">
+        <v>76</v>
+      </c>
+      <c r="C64" t="s">
+        <v>94</v>
+      </c>
+      <c r="D64" s="3"/>
+      <c r="E64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" t="s">
+        <v>77</v>
+      </c>
+      <c r="C65" t="s">
+        <v>94</v>
+      </c>
+      <c r="D65" s="3"/>
+      <c r="E65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" t="s">
+        <v>78</v>
+      </c>
+      <c r="C66" t="s">
+        <v>94</v>
+      </c>
+      <c r="D66" s="3"/>
+      <c r="E66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" t="s">
+        <v>79</v>
+      </c>
+      <c r="C67" t="s">
+        <v>94</v>
+      </c>
+      <c r="D67" s="3"/>
+      <c r="E67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" t="s">
+        <v>80</v>
+      </c>
+      <c r="C68" t="s">
+        <v>94</v>
+      </c>
+      <c r="D68" s="3"/>
+      <c r="E68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" t="s">
+        <v>81</v>
+      </c>
+      <c r="C69" t="s">
+        <v>94</v>
+      </c>
+      <c r="D69" s="3"/>
+      <c r="E69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>82</v>
+      </c>
+      <c r="C70" t="s">
+        <v>94</v>
+      </c>
+      <c r="D70" s="3"/>
+      <c r="E70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>4</v>
+      </c>
+      <c r="B71" t="s">
+        <v>83</v>
+      </c>
+      <c r="C71" t="s">
+        <v>94</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" t="s">
+        <v>84</v>
+      </c>
+      <c r="C72" t="s">
+        <v>94</v>
+      </c>
+      <c r="D72" s="3"/>
+      <c r="E72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>4</v>
+      </c>
+      <c r="B73" t="s">
+        <v>85</v>
+      </c>
+      <c r="C73" t="s">
+        <v>94</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="E73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" t="s">
+        <v>86</v>
+      </c>
+      <c r="C74" t="s">
+        <v>94</v>
+      </c>
+      <c r="D74" s="3"/>
+      <c r="E74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75" t="s">
+        <v>87</v>
+      </c>
+      <c r="C75" t="s">
+        <v>94</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="E75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" t="s">
+        <v>88</v>
+      </c>
+      <c r="C76" t="s">
+        <v>94</v>
+      </c>
+      <c r="D76" s="3"/>
+      <c r="E76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" t="s">
+        <v>89</v>
+      </c>
+      <c r="C77" t="s">
+        <v>94</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="E77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>90</v>
+      </c>
+      <c r="C78" t="s">
+        <v>94</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" t="s">
+        <v>91</v>
+      </c>
+      <c r="C79" t="s">
+        <v>94</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+    </row>
+    <row r="81" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+    </row>
+    <row r="82" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+    </row>
+    <row r="83" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+    </row>
+    <row r="84" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+    </row>
+    <row r="85" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+    </row>
+    <row r="86" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+    </row>
+    <row r="87" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+    </row>
+    <row r="88" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+    </row>
+    <row r="89" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+    </row>
+    <row r="90" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+    </row>
+    <row r="91" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+    </row>
+    <row r="92" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+    </row>
+    <row r="93" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+    </row>
+    <row r="94" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+    </row>
+    <row r="95" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+    </row>
+    <row r="96" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+    </row>
+    <row r="97" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+    </row>
+    <row r="98" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+    </row>
+    <row r="99" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+    </row>
+    <row r="100" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+    </row>
+    <row r="101" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+    </row>
+    <row r="102" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+    </row>
+    <row r="103" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+    </row>
+    <row r="104" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+    </row>
+    <row r="105" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+    </row>
+    <row r="106" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+    </row>
+    <row r="107" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+    </row>
+    <row r="108" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+    </row>
+    <row r="109" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+    </row>
+    <row r="110" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+    </row>
+    <row r="111" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+    </row>
+    <row r="112" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+    </row>
+    <row r="113" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+    </row>
+    <row r="114" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+    </row>
+    <row r="115" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+    </row>
+    <row r="116" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+    </row>
+    <row r="117" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+    </row>
+    <row r="118" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+    </row>
+    <row r="119" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+    </row>
+    <row r="120" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+    </row>
+    <row r="121" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+    </row>
+    <row r="122" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+    </row>
+    <row r="123" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+    </row>
+    <row r="124" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+    </row>
+    <row r="125" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+    </row>
+    <row r="126" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+    </row>
+    <row r="127" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+    </row>
+    <row r="128" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+    </row>
+    <row r="129" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+    </row>
+    <row r="130" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+    </row>
+    <row r="131" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+    </row>
+    <row r="132" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+    </row>
+    <row r="133" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+    </row>
+    <row r="134" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+    </row>
+    <row r="135" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+    </row>
+    <row r="136" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+    </row>
+    <row r="137" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
+    </row>
+    <row r="138" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+    </row>
+    <row r="139" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D139" s="3"/>
+      <c r="E139" s="3"/>
+    </row>
+    <row r="140" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+    </row>
+    <row r="141" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+    </row>
+    <row r="142" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+    </row>
+    <row r="143" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+    </row>
+    <row r="144" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+    </row>
+    <row r="145" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D145" s="3"/>
+      <c r="E145" s="3"/>
+    </row>
+    <row r="146" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+    </row>
+    <row r="147" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+    </row>
+    <row r="148" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+    </row>
+    <row r="149" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D149" s="3"/>
+      <c r="E149" s="3"/>
+    </row>
+    <row r="150" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D150" s="3"/>
+      <c r="E150" s="3"/>
+    </row>
+    <row r="151" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+    </row>
+    <row r="152" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+    </row>
+    <row r="153" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D153" s="3"/>
+      <c r="E153" s="3"/>
+    </row>
+    <row r="154" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+    </row>
+    <row r="155" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D155" s="3"/>
+      <c r="E155" s="3"/>
+    </row>
+    <row r="156" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+    </row>
+    <row r="157" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+    </row>
+    <row r="158" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+    </row>
+    <row r="159" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D159" s="3"/>
+      <c r="E159" s="3"/>
+    </row>
+    <row r="160" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+    </row>
+    <row r="161" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D161" s="3"/>
+      <c r="E161" s="3"/>
+    </row>
+    <row r="162" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D162" s="3"/>
+      <c r="E162" s="3"/>
+    </row>
+    <row r="163" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D163" s="3"/>
+      <c r="E163" s="3"/>
+    </row>
+    <row r="164" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+    </row>
+    <row r="165" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D165" s="3"/>
+      <c r="E165" s="3"/>
+    </row>
+    <row r="166" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+    </row>
+    <row r="167" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D167" s="3"/>
+      <c r="E167" s="3"/>
+    </row>
+    <row r="168" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D168" s="3"/>
+      <c r="E168" s="3"/>
+    </row>
+    <row r="169" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D169" s="3"/>
+      <c r="E169" s="3"/>
+    </row>
+    <row r="170" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D170" s="3"/>
+      <c r="E170" s="3"/>
+    </row>
+    <row r="171" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D171" s="3"/>
+      <c r="E171" s="3"/>
+    </row>
+    <row r="172" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D172" s="3"/>
+      <c r="E172" s="3"/>
+    </row>
+    <row r="173" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D173" s="3"/>
+      <c r="E173" s="3"/>
+    </row>
+    <row r="174" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D174" s="3"/>
+      <c r="E174" s="3"/>
+    </row>
+    <row r="175" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D175" s="3"/>
+      <c r="E175" s="3"/>
+    </row>
+    <row r="176" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D176" s="3"/>
+      <c r="E176" s="3"/>
+    </row>
+    <row r="177" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D177" s="3"/>
+      <c r="E177" s="3"/>
+    </row>
+    <row r="178" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D178" s="3"/>
+      <c r="E178" s="3"/>
+    </row>
+    <row r="179" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D179" s="3"/>
+      <c r="E179" s="3"/>
+    </row>
+    <row r="180" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D180" s="3"/>
+      <c r="E180" s="3"/>
+    </row>
+    <row r="181" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D181" s="3"/>
+      <c r="E181" s="3"/>
+    </row>
+    <row r="182" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D182" s="3"/>
+      <c r="E182" s="3"/>
+    </row>
+    <row r="183" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D183" s="3"/>
+      <c r="E183" s="3"/>
+    </row>
+    <row r="184" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D184" s="3"/>
+      <c r="E184" s="3"/>
+    </row>
+    <row r="185" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D185" s="3"/>
+      <c r="E185" s="3"/>
+    </row>
+    <row r="186" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D186" s="3"/>
+      <c r="E186" s="3"/>
+    </row>
+    <row r="187" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D187" s="3"/>
+      <c r="E187" s="3"/>
+    </row>
+    <row r="188" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D188" s="3"/>
+      <c r="E188" s="3"/>
+    </row>
+    <row r="189" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D189" s="3"/>
+      <c r="E189" s="3"/>
+    </row>
+    <row r="190" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D190" s="3"/>
+      <c r="E190" s="3"/>
+    </row>
+    <row r="191" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D191" s="3"/>
+      <c r="E191" s="3"/>
+    </row>
+    <row r="192" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D192" s="3"/>
+      <c r="E192" s="3"/>
+    </row>
+    <row r="193" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D193" s="3"/>
+      <c r="E193" s="3"/>
+    </row>
+    <row r="194" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D194" s="3"/>
+      <c r="E194" s="3"/>
+    </row>
+    <row r="195" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D195" s="3"/>
+      <c r="E195" s="3"/>
+    </row>
+    <row r="196" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D196" s="3"/>
+      <c r="E196" s="3"/>
+    </row>
+    <row r="197" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D197" s="3"/>
+      <c r="E197" s="3"/>
+    </row>
+    <row r="198" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D198" s="3"/>
+      <c r="E198" s="3"/>
+    </row>
+    <row r="199" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D199" s="3"/>
+      <c r="E199" s="3"/>
+    </row>
+    <row r="200" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D200" s="3"/>
+      <c r="E200" s="3"/>
+    </row>
+    <row r="201" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D201" s="3"/>
+      <c r="E201" s="3"/>
+    </row>
+    <row r="202" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D202" s="3"/>
+      <c r="E202" s="3"/>
+    </row>
+    <row r="203" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D203" s="3"/>
+      <c r="E203" s="3"/>
+    </row>
+    <row r="204" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D204" s="3"/>
+      <c r="E204" s="3"/>
+    </row>
+    <row r="205" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D205" s="3"/>
+      <c r="E205" s="3"/>
+    </row>
+    <row r="206" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D206" s="3"/>
+      <c r="E206" s="3"/>
+    </row>
+    <row r="207" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D207" s="3"/>
+      <c r="E207" s="3"/>
+    </row>
+    <row r="208" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D208" s="3"/>
+      <c r="E208" s="3"/>
+    </row>
+    <row r="209" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D209" s="3"/>
+      <c r="E209" s="3"/>
+    </row>
+    <row r="210" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D210" s="3"/>
+      <c r="E210" s="3"/>
+    </row>
+    <row r="211" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D211" s="3"/>
+      <c r="E211" s="3"/>
+    </row>
+    <row r="212" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D212" s="3"/>
+      <c r="E212" s="3"/>
+    </row>
+    <row r="213" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D213" s="3"/>
+      <c r="E213" s="3"/>
+    </row>
+    <row r="214" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D214" s="3"/>
+      <c r="E214" s="3"/>
+    </row>
+    <row r="215" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D215" s="3"/>
+      <c r="E215" s="3"/>
+    </row>
+    <row r="216" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D216" s="3"/>
+      <c r="E216" s="3"/>
+    </row>
+    <row r="217" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D217" s="3"/>
+      <c r="E217" s="3"/>
+    </row>
+    <row r="218" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D218" s="3"/>
+      <c r="E218" s="3"/>
+    </row>
+    <row r="219" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D219" s="3"/>
+      <c r="E219" s="3"/>
+    </row>
+    <row r="220" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D220" s="3"/>
+      <c r="E220" s="3"/>
+    </row>
+    <row r="221" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D221" s="3"/>
+      <c r="E221" s="3"/>
+    </row>
+    <row r="222" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D222" s="3"/>
+      <c r="E222" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E222" xr:uid="{1BC8E976-27F5-4CF2-963C-1DA4DC754C80}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE9CE415-51F9-4D30-A40A-C82454A84B45}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="76.5" customWidth="1"/>
@@ -4697,13 +7289,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -4711,15 +7303,27 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B6" s="5"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B7" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{C7D1D5D5-F515-4AB3-B6A2-D64283BEC9DE}"/>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{C7D1D5D5-F515-4AB3-B6A2-D64283BEC9DE}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{E7148FE8-A2FC-4201-B1C0-F33DF25B71AE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/QLD_properties.xlsx
+++ b/data/QLD_properties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\UNIMELB\outbreaksimulator\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597368DF-7C46-46E7-9311-57C93CA2FC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E13113-E59A-4902-BF57-93E85308F557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E264DCFB-2E54-41D3-AA9C-B1867134B6AE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="105">
   <si>
     <t>Region Type</t>
   </si>
@@ -3360,7 +3360,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>7</v>
@@ -3377,7 +3377,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>7</v>
@@ -3394,7 +3394,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>7</v>
@@ -3411,7 +3411,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>7</v>
@@ -3428,7 +3428,7 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>7</v>
@@ -3445,7 +3445,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>7</v>
@@ -3462,7 +3462,7 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>7</v>
@@ -3479,7 +3479,7 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>7</v>
@@ -3496,7 +3496,7 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>7</v>
@@ -3513,7 +3513,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>7</v>
@@ -3530,7 +3530,7 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>7</v>
@@ -3547,7 +3547,7 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>7</v>
@@ -3564,7 +3564,7 @@
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>7</v>
@@ -3581,7 +3581,7 @@
         <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>7</v>
@@ -3598,7 +3598,7 @@
         <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>7</v>
@@ -3615,7 +3615,7 @@
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>7</v>
@@ -3632,7 +3632,7 @@
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>7</v>
@@ -3649,7 +3649,7 @@
         <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>7</v>
@@ -3666,7 +3666,7 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>7</v>
@@ -3683,7 +3683,7 @@
         <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>7</v>
@@ -3700,7 +3700,7 @@
         <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>7</v>
@@ -3717,7 +3717,7 @@
         <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>7</v>
@@ -3734,7 +3734,7 @@
         <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>7</v>
@@ -3751,7 +3751,7 @@
         <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>7</v>
@@ -3768,7 +3768,7 @@
         <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>7</v>
@@ -3785,7 +3785,7 @@
         <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>7</v>
@@ -3802,7 +3802,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>7</v>
@@ -3819,7 +3819,7 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>7</v>
@@ -3836,7 +3836,7 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>7</v>
@@ -3853,7 +3853,7 @@
         <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>7</v>
@@ -3870,7 +3870,7 @@
         <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>7</v>
@@ -3887,7 +3887,7 @@
         <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>7</v>
@@ -3904,7 +3904,7 @@
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>7</v>
@@ -3921,7 +3921,7 @@
         <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>7</v>
@@ -3938,7 +3938,7 @@
         <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>7</v>
@@ -3955,7 +3955,7 @@
         <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>7</v>
@@ -3972,7 +3972,7 @@
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>7</v>
@@ -3989,7 +3989,7 @@
         <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>7</v>
@@ -4006,7 +4006,7 @@
         <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>7</v>
@@ -4023,7 +4023,7 @@
         <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>7</v>
@@ -4040,7 +4040,7 @@
         <v>30</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>7</v>
@@ -4057,7 +4057,7 @@
         <v>31</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>7</v>
@@ -4074,7 +4074,7 @@
         <v>32</v>
       </c>
       <c r="C44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>7</v>
@@ -4091,7 +4091,7 @@
         <v>33</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>7</v>
@@ -4108,7 +4108,7 @@
         <v>34</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>7</v>
@@ -4125,7 +4125,7 @@
         <v>35</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>7</v>
@@ -4142,7 +4142,7 @@
         <v>36</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>7</v>
@@ -4159,7 +4159,7 @@
         <v>37</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>7</v>
@@ -4176,7 +4176,7 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>7</v>
@@ -4193,7 +4193,7 @@
         <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>7</v>
@@ -4210,7 +4210,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>7</v>
@@ -4227,7 +4227,7 @@
         <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>7</v>
@@ -4244,7 +4244,7 @@
         <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>7</v>
@@ -4261,7 +4261,7 @@
         <v>19</v>
       </c>
       <c r="C55" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>7</v>
@@ -4278,7 +4278,7 @@
         <v>20</v>
       </c>
       <c r="C56" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>7</v>
@@ -4295,7 +4295,7 @@
         <v>21</v>
       </c>
       <c r="C57" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>7</v>
@@ -4312,7 +4312,7 @@
         <v>22</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>7</v>
@@ -4329,7 +4329,7 @@
         <v>23</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>7</v>
@@ -4346,7 +4346,7 @@
         <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>7</v>
@@ -4363,7 +4363,7 @@
         <v>25</v>
       </c>
       <c r="C61" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>7</v>
@@ -4380,7 +4380,7 @@
         <v>26</v>
       </c>
       <c r="C62" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>7</v>
@@ -4397,7 +4397,7 @@
         <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>7</v>
@@ -4414,7 +4414,7 @@
         <v>28</v>
       </c>
       <c r="C64" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>7</v>
@@ -4431,7 +4431,7 @@
         <v>29</v>
       </c>
       <c r="C65" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>7</v>
@@ -4448,7 +4448,7 @@
         <v>30</v>
       </c>
       <c r="C66" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>7</v>
@@ -4465,7 +4465,7 @@
         <v>31</v>
       </c>
       <c r="C67" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>7</v>
@@ -4482,7 +4482,7 @@
         <v>32</v>
       </c>
       <c r="C68" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>7</v>
@@ -4499,7 +4499,7 @@
         <v>33</v>
       </c>
       <c r="C69" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>7</v>
@@ -4516,7 +4516,7 @@
         <v>34</v>
       </c>
       <c r="C70" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>7</v>
@@ -4533,7 +4533,7 @@
         <v>35</v>
       </c>
       <c r="C71" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>7</v>
@@ -4550,7 +4550,7 @@
         <v>36</v>
       </c>
       <c r="C72" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>7</v>
@@ -4567,7 +4567,7 @@
         <v>37</v>
       </c>
       <c r="C73" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>7</v>
@@ -4576,471 +4576,63 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>4</v>
-      </c>
-      <c r="B74" t="s">
-        <v>14</v>
-      </c>
-      <c r="C74" t="s">
-        <v>96</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E74" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>4</v>
-      </c>
-      <c r="B75" t="s">
-        <v>15</v>
-      </c>
-      <c r="C75" t="s">
-        <v>96</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E75" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>4</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="s">
-        <v>96</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E76" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>4</v>
-      </c>
-      <c r="B77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C77" t="s">
-        <v>96</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E77" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>4</v>
-      </c>
-      <c r="B78" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" t="s">
-        <v>96</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E78" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>4</v>
-      </c>
-      <c r="B79" t="s">
-        <v>19</v>
-      </c>
-      <c r="C79" t="s">
-        <v>96</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E79" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>4</v>
-      </c>
-      <c r="B80" t="s">
-        <v>20</v>
-      </c>
-      <c r="C80" t="s">
-        <v>96</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E80" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>4</v>
-      </c>
-      <c r="B81" t="s">
-        <v>21</v>
-      </c>
-      <c r="C81" t="s">
-        <v>96</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>4</v>
-      </c>
-      <c r="B82" t="s">
-        <v>22</v>
-      </c>
-      <c r="C82" t="s">
-        <v>96</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E82" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>4</v>
-      </c>
-      <c r="B83" t="s">
-        <v>23</v>
-      </c>
-      <c r="C83" t="s">
-        <v>96</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>4</v>
-      </c>
-      <c r="B84" t="s">
-        <v>24</v>
-      </c>
-      <c r="C84" t="s">
-        <v>96</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E84" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>4</v>
-      </c>
-      <c r="B85" t="s">
-        <v>25</v>
-      </c>
-      <c r="C85" t="s">
-        <v>96</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E85" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>4</v>
-      </c>
-      <c r="B86" t="s">
-        <v>26</v>
-      </c>
-      <c r="C86" t="s">
-        <v>96</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E86" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>4</v>
-      </c>
-      <c r="B87" t="s">
-        <v>27</v>
-      </c>
-      <c r="C87" t="s">
-        <v>96</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E87" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>4</v>
-      </c>
-      <c r="B88" t="s">
-        <v>28</v>
-      </c>
-      <c r="C88" t="s">
-        <v>96</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E88" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>4</v>
-      </c>
-      <c r="B89" t="s">
-        <v>29</v>
-      </c>
-      <c r="C89" t="s">
-        <v>96</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E89" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>4</v>
-      </c>
-      <c r="B90" t="s">
-        <v>30</v>
-      </c>
-      <c r="C90" t="s">
-        <v>96</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E90" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>4</v>
-      </c>
-      <c r="B91" t="s">
-        <v>31</v>
-      </c>
-      <c r="C91" t="s">
-        <v>96</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E91" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>4</v>
-      </c>
-      <c r="B92" t="s">
-        <v>32</v>
-      </c>
-      <c r="C92" t="s">
-        <v>96</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E92" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>4</v>
-      </c>
-      <c r="B93" t="s">
-        <v>33</v>
-      </c>
-      <c r="C93" t="s">
-        <v>96</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E93" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>4</v>
-      </c>
-      <c r="B94" t="s">
-        <v>34</v>
-      </c>
-      <c r="C94" t="s">
-        <v>96</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E94" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>4</v>
-      </c>
-      <c r="B95" t="s">
-        <v>35</v>
-      </c>
-      <c r="C95" t="s">
-        <v>96</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E95" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>4</v>
-      </c>
-      <c r="B96" t="s">
-        <v>36</v>
-      </c>
-      <c r="C96" t="s">
-        <v>96</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E96" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>4</v>
-      </c>
-      <c r="B97" t="s">
-        <v>37</v>
-      </c>
-      <c r="C97" t="s">
-        <v>96</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E97" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
     </row>
